--- a/course-design-2/outputs/tables/ch7/48_stage26_3_pre_model_diagnostics.xlsx
+++ b/course-design-2/outputs/tables/ch7/48_stage26_3_pre_model_diagnostics.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_缺失率" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_近常量与低方差" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_低频类别" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_稀有标签与低频技能" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_连续数值特征冗余对" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Spearman相关矩阵" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_三子集分布对照" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_移除特征清单" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="01_缺失率" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="02_近常量与低方差" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="03_低频类别" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="04_稀有标签与低频技能" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="05_连续数值特征冗余对" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="06_Spearman相关矩阵" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="07_三子集分布对照" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="08_移除特征清单" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2976,7 +2976,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>技能主/扩展口径可命中技能条目数</t>
+          <t>技能主/扩展统计范围可命中技能条目数</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -3016,7 +3016,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>阈值口径</t>
+          <t>阈值设定</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">

--- a/course-design-2/outputs/tables/ch7/48_stage26_3_pre_model_diagnostics.xlsx
+++ b/course-design-2/outputs/tables/ch7/48_stage26_3_pre_model_diagnostics.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="01_缺失率" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="02_近常量与低方差" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="03_低频类别" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="04_稀有标签与低频技能" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="05_连续数值特征冗余对" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="06_Spearman相关矩阵" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="07_三子集分布对照" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="08_移除特征清单" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_缺失率" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_近常量与低方差" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_低频类别" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_稀有标签与低频技能" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_连续数值特征冗余对" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Spearman相关矩阵" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_三子集分布对照" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_移除特征清单" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2976,7 +2976,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>技能主/扩展统计范围可命中技能条目数</t>
+          <t>技能主/扩展口径可命中技能条目数</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -3016,7 +3016,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>阈值设定</t>
+          <t>阈值口径</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
